--- a/Assets/Data/Classic-Repair-Toolbox.v2.0.0.xlsx
+++ b/Assets/Data/Classic-Repair-Toolbox.v2.0.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dennis\AppData\Local\Classic-Repair-Toolbox\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F6BB584-7EB8-47F5-9F05-321D8762DB80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8538DF07-446C-4092-A467-ECD73AD1A6BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{EBC5E150-CC27-441B-9E4F-9F7CF77570D6}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{EBC5E150-CC27-441B-9E4F-9F7CF77570D6}"/>
   </bookViews>
   <sheets>
     <sheet name="Hardware &amp; Board" sheetId="1" r:id="rId1"/>
@@ -502,6 +502,33 @@
     <t>8-pin audio/video port.</t>
   </si>
   <si>
+    <t>Amstrad/CPC 664/MC0005A/Data CPC 664 MC0005A v2.0.0.xlsx</t>
+  </si>
+  <si>
+    <t>Commodore/VIC-20/250403/Data VIC20 250403 v2.0.0.xlsx</t>
+  </si>
+  <si>
+    <t>Commodore/C64/KU-14194HB/Data C64 KU-14194HB v2.0.0.xlsx</t>
+  </si>
+  <si>
+    <t>Commodore/C64/250407/Data C64 250407 v2.0.0.xlsx</t>
+  </si>
+  <si>
+    <t>Commodore/C64/250425/Data C64 250425 v2.0.0.xlsx</t>
+  </si>
+  <si>
+    <t>Commodore/C64/250466/Data C64 250466 v2.0.0.xlsx</t>
+  </si>
+  <si>
+    <t>Commodore/C64/250469/Data C64 250469 v2.0.0.xlsx</t>
+  </si>
+  <si>
+    <t>Commodore/C128/310378/Data C128 310378 v2.0.0.xlsx</t>
+  </si>
+  <si>
+    <t>Commodore/C128/250477/Data C128DCR 250477 v2.0.0.xlsx</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve"># Revision date: </t>
     </r>
@@ -514,35 +541,8 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>2026-May-7</t>
+      <t>2026-May-12</t>
     </r>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/Data CPC 664 MC0005A v2.0.0.xlsx</t>
-  </si>
-  <si>
-    <t>Commodore VIC-20/250403/Data VIC20 250403 v2.0.0.xlsx</t>
-  </si>
-  <si>
-    <t>Commodore 64/KU-14194HB/Data C64 KU-14194HB v2.0.0.xlsx</t>
-  </si>
-  <si>
-    <t>Commodore 64/250407/Data C64 250407 v2.0.0.xlsx</t>
-  </si>
-  <si>
-    <t>Commodore 64/250425/Data C64 250425 v2.0.0.xlsx</t>
-  </si>
-  <si>
-    <t>Commodore 64/250466/Data C64 250466 v2.0.0.xlsx</t>
-  </si>
-  <si>
-    <t>Commodore 64/250469/Data C64 250469 v2.0.0.xlsx</t>
-  </si>
-  <si>
-    <t>Commodore 128/310378/Data C128 310378 v2.0.0.xlsx</t>
-  </si>
-  <si>
-    <t>Commodore 128/250477/Data C128DCR 250477 v2.0.0.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1054,7 +1054,7 @@
     </row>
     <row r="3" spans="1:4" s="2" customFormat="1" ht="21" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -1097,7 +1097,7 @@
         <v>20</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>21</v>
@@ -1111,7 +1111,7 @@
         <v>8</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>147</v>
@@ -1125,7 +1125,7 @@
         <v>141</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>142</v>
@@ -1139,7 +1139,7 @@
         <v>16</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>142</v>
@@ -1153,7 +1153,7 @@
         <v>17</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>142</v>
@@ -1167,7 +1167,7 @@
         <v>18</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>143</v>
@@ -1181,7 +1181,7 @@
         <v>15</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>146</v>
@@ -1195,7 +1195,7 @@
         <v>12</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>144</v>
@@ -1209,7 +1209,7 @@
         <v>13</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>145</v>

--- a/Assets/Data/Classic-Repair-Toolbox.v2.0.0.xlsx
+++ b/Assets/Data/Classic-Repair-Toolbox.v2.0.0.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dennis\AppData\Local\Classic-Repair-Toolbox\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.20.10\all\mydir\http\classic-repair-toolbox.dk\public_html\app-data\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8538DF07-446C-4092-A467-ECD73AD1A6BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{302347FF-7C35-4E67-B3A9-AB33CA46F6F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{EBC5E150-CC27-441B-9E4F-9F7CF77570D6}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{EBC5E150-CC27-441B-9E4F-9F7CF77570D6}"/>
   </bookViews>
   <sheets>
     <sheet name="Hardware &amp; Board" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="724" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="161">
   <si>
     <t>Hardware name in drop-down</t>
   </si>
@@ -529,6 +529,15 @@
     <t>Commodore/C128/250477/Data C128DCR 250477 v2.0.0.xlsx</t>
   </si>
   <si>
+    <t>ZX Spectrum 16K/48K</t>
+  </si>
+  <si>
+    <t>Issue 4B</t>
+  </si>
+  <si>
+    <t>ZX Spectrum/Spectrum 16K-48K/Issue 4B/Data ZX 4B v2.0.0.xlsx</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve"># Revision date: </t>
     </r>
@@ -541,7 +550,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>2026-May-12</t>
+      <t>2026-May-16</t>
     </r>
   </si>
 </sst>
@@ -1054,7 +1063,7 @@
     </row>
     <row r="3" spans="1:4" s="2" customFormat="1" ht="21" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -1215,8 +1224,16 @@
         <v>145</v>
       </c>
     </row>
-    <row r="19" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="9"/>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="20" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="21" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">

--- a/Assets/Data/Classic-Repair-Toolbox.v2.0.0.xlsx
+++ b/Assets/Data/Classic-Repair-Toolbox.v2.0.0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.20.10\all\mydir\http\classic-repair-toolbox.dk\public_html\app-data\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{302347FF-7C35-4E67-B3A9-AB33CA46F6F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C4B03D5-A29A-475B-A433-A5E1B5038D31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{EBC5E150-CC27-441B-9E4F-9F7CF77570D6}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{EBC5E150-CC27-441B-9E4F-9F7CF77570D6}"/>
   </bookViews>
   <sheets>
     <sheet name="Hardware &amp; Board" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="169">
   <si>
     <t>Hardware name in drop-down</t>
   </si>
@@ -485,57 +485,82 @@
 Has 6581 SID.</t>
   </si>
   <si>
-    <t>8-pin audio/video port..
+    <t>8-pin audio/video port.</t>
+  </si>
+  <si>
+    <t>Amstrad/CPC 664/MC0005A/Data CPC 664 MC0005A v2.0.0.xlsx</t>
+  </si>
+  <si>
+    <t>Commodore/VIC-20/250403/Data VIC20 250403 v2.0.0.xlsx</t>
+  </si>
+  <si>
+    <t>Commodore/C64/KU-14194HB/Data C64 KU-14194HB v2.0.0.xlsx</t>
+  </si>
+  <si>
+    <t>Commodore/C64/250407/Data C64 250407 v2.0.0.xlsx</t>
+  </si>
+  <si>
+    <t>Commodore/C64/250425/Data C64 250425 v2.0.0.xlsx</t>
+  </si>
+  <si>
+    <t>Commodore/C64/250466/Data C64 250466 v2.0.0.xlsx</t>
+  </si>
+  <si>
+    <t>Commodore/C64/250469/Data C64 250469 v2.0.0.xlsx</t>
+  </si>
+  <si>
+    <t>Commodore/C128/310378/Data C128 310378 v2.0.0.xlsx</t>
+  </si>
+  <si>
+    <t>Commodore/C128/250477/Data C128DCR 250477 v2.0.0.xlsx</t>
+  </si>
+  <si>
+    <t>ZX Spectrum 16K/48K</t>
+  </si>
+  <si>
+    <t>Issue 4B</t>
+  </si>
+  <si>
+    <t>ZX Spectrum/Spectrum 16K-48K/Issue 4B/Data ZX 4B v2.0.0.xlsx</t>
+  </si>
+  <si>
+    <t>Commodore/VIC-20/324003/Data VIC20 324003 v2.0.0.xlsx</t>
+  </si>
+  <si>
+    <t>5-pin audio/video port.</t>
+  </si>
+  <si>
+    <t>Commodore/Plus4/310163/Data Plus4 310163 v2.0.0.xlsx</t>
+  </si>
+  <si>
+    <t>8-pin audio/video port.
+Black wedge case.</t>
+  </si>
+  <si>
+    <t>Commodore Plus/4</t>
+  </si>
+  <si>
+    <t>8-pin audio/video port.
+Has 8580 SID.
+This is with the metal cabinet.</t>
+  </si>
+  <si>
+    <t>8-pin audio/video port.
 Has 6581 SID.
 C128D is with the plastic cabinet.</t>
   </si>
   <si>
-    <t>8-pin audio/video port..
-Has 8580 SID.
-This is with the metal cabinet.</t>
-  </si>
-  <si>
-    <t>8-pin audio/video port..
+    <t>8-pin audio/video port.
 Introduced SuperPLA and 8580 SID.</t>
   </si>
   <si>
-    <t>8-pin audio/video port.</t>
-  </si>
-  <si>
-    <t>Amstrad/CPC 664/MC0005A/Data CPC 664 MC0005A v2.0.0.xlsx</t>
-  </si>
-  <si>
-    <t>Commodore/VIC-20/250403/Data VIC20 250403 v2.0.0.xlsx</t>
-  </si>
-  <si>
-    <t>Commodore/C64/KU-14194HB/Data C64 KU-14194HB v2.0.0.xlsx</t>
-  </si>
-  <si>
-    <t>Commodore/C64/250407/Data C64 250407 v2.0.0.xlsx</t>
-  </si>
-  <si>
-    <t>Commodore/C64/250425/Data C64 250425 v2.0.0.xlsx</t>
-  </si>
-  <si>
-    <t>Commodore/C64/250466/Data C64 250466 v2.0.0.xlsx</t>
-  </si>
-  <si>
-    <t>Commodore/C64/250469/Data C64 250469 v2.0.0.xlsx</t>
-  </si>
-  <si>
-    <t>Commodore/C128/310378/Data C128 310378 v2.0.0.xlsx</t>
-  </si>
-  <si>
-    <t>Commodore/C128/250477/Data C128DCR 250477 v2.0.0.xlsx</t>
-  </si>
-  <si>
-    <t>ZX Spectrum 16K/48K</t>
-  </si>
-  <si>
-    <t>Issue 4B</t>
-  </si>
-  <si>
-    <t>ZX Spectrum/Spectrum 16K-48K/Issue 4B/Data ZX 4B v2.0.0.xlsx</t>
+    <t>Commodore 16</t>
+  </si>
+  <si>
+    <t>Commodore/C16/251789/Data C16 251789 v2.0.0.xlsx</t>
+  </si>
+  <si>
+    <t>?</t>
   </si>
   <si>
     <r>
@@ -550,7 +575,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>2026-May-16</t>
+      <t>2026-July-13</t>
     </r>
   </si>
 </sst>
@@ -1040,7 +1065,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1251FF9-425C-410E-B269-C7726F9C2504}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:D70"/>
+  <dimension ref="A1:D73"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="31.5546875" style="5" customWidth="1"/>
@@ -1063,7 +1088,7 @@
     </row>
     <row r="3" spans="1:4" s="2" customFormat="1" ht="21" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -1106,80 +1131,80 @@
         <v>20</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B11" s="1">
+        <v>310163</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B12" s="1">
+        <v>324003</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="C13" s="1" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>17</v>
+        <v>165</v>
+      </c>
+      <c r="B14" s="1">
+        <v>251789</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>18</v>
+        <v>141</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
@@ -1187,71 +1212,108 @@
         <v>9</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C19" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C17" s="1" t="s">
+      <c r="B22" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="D17" s="1" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C18" s="1" t="s">
+      <c r="C22" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="21" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="8"/>
-    </row>
-    <row r="22" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3"/>
+    </row>
     <row r="23" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="24" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="25" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="8"/>
-    </row>
+    <row r="24" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="8"/>
+    </row>
+    <row r="25" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="26" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="27" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="28" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="8"/>
+    </row>
     <row r="29" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="30" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="8"/>
-    </row>
+    <row r="30" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="31" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="32" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="33" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -1260,14 +1322,10 @@
     <row r="34" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="35" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="36" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="7"/>
-    </row>
-    <row r="37" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="7"/>
-    </row>
-    <row r="38" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="7"/>
-    </row>
+      <c r="A36" s="8"/>
+    </row>
+    <row r="37" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="38" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="39" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A39" s="7"/>
     </row>
@@ -1363,6 +1421,15 @@
     </row>
     <row r="70" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A70" s="7"/>
+    </row>
+    <row r="71" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="7"/>
+    </row>
+    <row r="72" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="7"/>
+    </row>
+    <row r="73" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="7"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/Assets/Data/Classic-Repair-Toolbox.v2.0.0.xlsx
+++ b/Assets/Data/Classic-Repair-Toolbox.v2.0.0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.20.10\all\mydir\http\classic-repair-toolbox.dk\public_html\app-data\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dennis\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C4B03D5-A29A-475B-A433-A5E1B5038D31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3DB73C1-FF5D-41AC-B6C1-322CEF8919A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{EBC5E150-CC27-441B-9E4F-9F7CF77570D6}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{EBC5E150-CC27-441B-9E4F-9F7CF77570D6}"/>
   </bookViews>
   <sheets>
     <sheet name="Hardware &amp; Board" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="171">
   <si>
     <t>Hardware name in drop-down</t>
   </si>
@@ -575,15 +575,21 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>2026-July-13</t>
+      <t>2026-August-7</t>
     </r>
+  </si>
+  <si>
+    <t>DHO800</t>
+  </si>
+  <si>
+    <t>DHO900</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -655,12 +661,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FFA31515"/>
-      <name val="Cascadia Mono"/>
-      <family val="3"/>
-    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -695,7 +695,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -745,9 +745,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1442,7 +1439,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56206CAE-0631-4609-AB22-50D6669B86E2}">
-  <dimension ref="A1:AF39"/>
+  <dimension ref="A1:AF41"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.33203125" customWidth="1"/>
@@ -1815,7 +1812,7 @@
       <c r="L9" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="M9" s="18" t="s">
+      <c r="M9" s="14" t="s">
         <v>105</v>
       </c>
       <c r="N9" s="14" t="s">
@@ -1987,7 +1984,7 @@
         <v>79</v>
       </c>
       <c r="B12" t="s">
-        <v>81</v>
+        <v>169</v>
       </c>
       <c r="C12">
         <v>5555</v>
@@ -2055,7 +2052,7 @@
         <v>79</v>
       </c>
       <c r="B13" t="s">
-        <v>82</v>
+        <v>170</v>
       </c>
       <c r="C13">
         <v>5555</v>
@@ -2123,7 +2120,7 @@
         <v>79</v>
       </c>
       <c r="B14" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C14">
         <v>5555</v>
@@ -2191,7 +2188,7 @@
         <v>79</v>
       </c>
       <c r="B15" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C15">
         <v>5555</v>
@@ -2259,7 +2256,7 @@
         <v>79</v>
       </c>
       <c r="B16" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C16">
         <v>5555</v>
@@ -2327,7 +2324,7 @@
         <v>79</v>
       </c>
       <c r="B17" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C17">
         <v>5555</v>
@@ -2392,13 +2389,13 @@
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>126</v>
+        <v>79</v>
       </c>
       <c r="B18" t="s">
-        <v>127</v>
+        <v>85</v>
       </c>
       <c r="C18">
-        <v>5025</v>
+        <v>5555</v>
       </c>
       <c r="D18" s="17" t="s">
         <v>115</v>
@@ -2407,13 +2404,13 @@
         <v>61</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>129</v>
+        <v>99</v>
       </c>
       <c r="G18" s="14" t="s">
         <v>63</v>
       </c>
       <c r="H18" s="14" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="I18" s="14" t="s">
         <v>101</v>
@@ -2428,45 +2425,45 @@
         <v>104</v>
       </c>
       <c r="M18" s="14" t="s">
-        <v>131</v>
+        <v>105</v>
       </c>
       <c r="N18" s="14" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="O18" s="14" t="s">
-        <v>133</v>
+        <v>107</v>
       </c>
       <c r="P18" s="14" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="Q18" s="14" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="R18" s="14" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="S18" s="14" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="T18" s="14" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="U18" s="14" t="s">
         <v>90</v>
       </c>
       <c r="V18" s="14" t="s">
-        <v>121</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>126</v>
+        <v>79</v>
       </c>
       <c r="B19" t="s">
-        <v>128</v>
+        <v>80</v>
       </c>
       <c r="C19">
-        <v>5025</v>
+        <v>5555</v>
       </c>
       <c r="D19" s="17" t="s">
         <v>115</v>
@@ -2475,63 +2472,63 @@
         <v>61</v>
       </c>
       <c r="F19" s="14" t="s">
-        <v>129</v>
+        <v>99</v>
       </c>
       <c r="G19" s="14" t="s">
         <v>63</v>
       </c>
       <c r="H19" s="14" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="I19" s="14" t="s">
-        <v>135</v>
+        <v>101</v>
       </c>
       <c r="J19" s="14" t="s">
-        <v>66</v>
+        <v>102</v>
       </c>
       <c r="K19" s="14" t="s">
-        <v>136</v>
+        <v>103</v>
       </c>
       <c r="L19" s="14" t="s">
-        <v>137</v>
+        <v>104</v>
       </c>
       <c r="M19" s="14" t="s">
-        <v>138</v>
+        <v>105</v>
       </c>
       <c r="N19" s="14" t="s">
-        <v>139</v>
+        <v>106</v>
       </c>
       <c r="O19" s="14" t="s">
-        <v>140</v>
+        <v>107</v>
       </c>
       <c r="P19" s="14" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="Q19" s="14" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="R19" s="14" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="S19" s="14" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="T19" s="14" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="U19" s="14" t="s">
         <v>90</v>
       </c>
       <c r="V19" s="14" t="s">
-        <v>121</v>
+        <v>91</v>
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>25</v>
+        <v>126</v>
       </c>
       <c r="B20" t="s">
-        <v>28</v>
+        <v>127</v>
       </c>
       <c r="C20">
         <v>5025</v>
@@ -2543,34 +2540,34 @@
         <v>61</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>62</v>
+        <v>129</v>
       </c>
       <c r="G20" s="14" t="s">
         <v>63</v>
       </c>
       <c r="H20" s="14" t="s">
-        <v>64</v>
+        <v>130</v>
       </c>
       <c r="I20" s="14" t="s">
-        <v>65</v>
+        <v>101</v>
       </c>
       <c r="J20" s="14" t="s">
-        <v>66</v>
+        <v>102</v>
       </c>
       <c r="K20" s="14" t="s">
-        <v>67</v>
+        <v>103</v>
       </c>
       <c r="L20" s="14" t="s">
-        <v>68</v>
+        <v>104</v>
       </c>
       <c r="M20" s="14" t="s">
-        <v>69</v>
+        <v>131</v>
       </c>
       <c r="N20" s="14" t="s">
-        <v>92</v>
+        <v>132</v>
       </c>
       <c r="O20" s="14" t="s">
-        <v>93</v>
+        <v>133</v>
       </c>
       <c r="P20" s="14" t="s">
         <v>94</v>
@@ -2585,21 +2582,21 @@
         <v>97</v>
       </c>
       <c r="T20" s="14" t="s">
-        <v>98</v>
+        <v>134</v>
       </c>
       <c r="U20" s="14" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="V20" s="14" t="s">
-        <v>87</v>
+        <v>121</v>
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>25</v>
+        <v>126</v>
       </c>
       <c r="B21" t="s">
-        <v>29</v>
+        <v>128</v>
       </c>
       <c r="C21">
         <v>5025</v>
@@ -2611,55 +2608,55 @@
         <v>61</v>
       </c>
       <c r="F21" s="14" t="s">
-        <v>62</v>
+        <v>129</v>
       </c>
       <c r="G21" s="14" t="s">
         <v>63</v>
       </c>
       <c r="H21" s="14" t="s">
-        <v>64</v>
+        <v>130</v>
       </c>
       <c r="I21" s="14" t="s">
-        <v>65</v>
+        <v>135</v>
       </c>
       <c r="J21" s="14" t="s">
         <v>66</v>
       </c>
       <c r="K21" s="14" t="s">
-        <v>67</v>
+        <v>136</v>
       </c>
       <c r="L21" s="14" t="s">
-        <v>68</v>
+        <v>137</v>
       </c>
       <c r="M21" s="14" t="s">
-        <v>69</v>
+        <v>138</v>
       </c>
       <c r="N21" s="14" t="s">
-        <v>70</v>
+        <v>139</v>
       </c>
       <c r="O21" s="14" t="s">
-        <v>71</v>
+        <v>140</v>
       </c>
       <c r="P21" s="14" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="Q21" s="14" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="R21" s="14" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="S21" s="14" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="T21" s="14" t="s">
-        <v>76</v>
+        <v>134</v>
       </c>
       <c r="U21" s="14" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="V21" s="14" t="s">
-        <v>87</v>
+        <v>121</v>
       </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.3">
@@ -2667,7 +2664,7 @@
         <v>25</v>
       </c>
       <c r="B22" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C22">
         <v>5025</v>
@@ -2703,25 +2700,25 @@
         <v>69</v>
       </c>
       <c r="N22" s="14" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="O22" s="14" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="P22" s="14" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="Q22" s="14" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="R22" s="14" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="S22" s="14" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="T22" s="14" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="U22" s="14" t="s">
         <v>86</v>
@@ -2735,7 +2732,7 @@
         <v>25</v>
       </c>
       <c r="B23" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C23">
         <v>5025</v>
@@ -2803,7 +2800,7 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C24">
         <v>5025</v>
@@ -2871,7 +2868,7 @@
         <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C25">
         <v>5025</v>
@@ -2939,7 +2936,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C26">
         <v>5025</v>
@@ -3007,7 +3004,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C27">
         <v>5025</v>
@@ -3043,25 +3040,25 @@
         <v>69</v>
       </c>
       <c r="N27" s="14" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="O27" s="14" t="s">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="P27" s="14" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="Q27" s="14" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="R27" s="14" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="S27" s="14" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="T27" s="14" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="U27" s="14" t="s">
         <v>86</v>
@@ -3075,7 +3072,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C28">
         <v>5025</v>
@@ -3123,10 +3120,10 @@
         <v>73</v>
       </c>
       <c r="R28" s="14" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="S28" s="14" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="T28" s="14" t="s">
         <v>76</v>
@@ -3143,7 +3140,7 @@
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C29">
         <v>5025</v>
@@ -3179,25 +3176,25 @@
         <v>69</v>
       </c>
       <c r="N29" s="14" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="O29" s="14" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="P29" s="14" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="Q29" s="14" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="R29" s="14" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="S29" s="14" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="T29" s="14" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="U29" s="14" t="s">
         <v>86</v>
@@ -3211,7 +3208,7 @@
         <v>25</v>
       </c>
       <c r="B30" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C30">
         <v>5025</v>
@@ -3247,25 +3244,25 @@
         <v>69</v>
       </c>
       <c r="N30" s="14" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="O30" s="14" t="s">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="P30" s="14" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="Q30" s="14" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="R30" s="14" t="s">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="S30" s="14" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="T30" s="14" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="U30" s="14" t="s">
         <v>86</v>
@@ -3279,7 +3276,7 @@
         <v>25</v>
       </c>
       <c r="B31" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C31">
         <v>5025</v>
@@ -3315,25 +3312,25 @@
         <v>69</v>
       </c>
       <c r="N31" s="14" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="O31" s="14" t="s">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="P31" s="14" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="Q31" s="14" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="R31" s="14" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="S31" s="14" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="T31" s="14" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="U31" s="14" t="s">
         <v>86</v>
@@ -3347,7 +3344,7 @@
         <v>25</v>
       </c>
       <c r="B32" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C32">
         <v>5025</v>
@@ -3415,7 +3412,7 @@
         <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C33">
         <v>5025</v>
@@ -3483,7 +3480,7 @@
         <v>25</v>
       </c>
       <c r="B34" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C34">
         <v>5025</v>
@@ -3551,7 +3548,7 @@
         <v>25</v>
       </c>
       <c r="B35" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C35">
         <v>5025</v>
@@ -3619,7 +3616,7 @@
         <v>25</v>
       </c>
       <c r="B36" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C36">
         <v>5025</v>
@@ -3687,7 +3684,7 @@
         <v>25</v>
       </c>
       <c r="B37" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C37">
         <v>5025</v>
@@ -3755,7 +3752,7 @@
         <v>25</v>
       </c>
       <c r="B38" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C38">
         <v>5025</v>
@@ -3823,7 +3820,7 @@
         <v>25</v>
       </c>
       <c r="B39" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="C39">
         <v>5025</v>
@@ -3883,6 +3880,142 @@
         <v>86</v>
       </c>
       <c r="V39" s="14" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="40" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>25</v>
+      </c>
+      <c r="B40" t="s">
+        <v>46</v>
+      </c>
+      <c r="C40">
+        <v>5025</v>
+      </c>
+      <c r="D40" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="E40" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="F40" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="G40" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="H40" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="I40" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="J40" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="K40" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="L40" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="M40" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="N40" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="O40" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="P40" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q40" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="R40" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="S40" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="T40" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="U40" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="V40" s="14" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="41" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>25</v>
+      </c>
+      <c r="B41" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41">
+        <v>5025</v>
+      </c>
+      <c r="D41" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="E41" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="F41" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="G41" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="H41" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="I41" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="J41" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="K41" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="L41" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="M41" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="N41" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="O41" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="P41" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q41" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="R41" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="S41" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="T41" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="U41" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="V41" s="14" t="s">
         <v>87</v>
       </c>
     </row>
